--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -514,7 +514,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>106.69</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>102.56</v>
+        <v>110.12</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>101.76</v>
+        <v>109.27</v>
       </c>
     </row>
     <row r="5">
@@ -565,7 +565,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>100.19</v>
+        <v>108.16</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>96.94</v>
+        <v>105.54</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>94.72</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>91.49</v>
+        <v>98.46</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>90.19</v>
+        <v>97.46</v>
       </c>
     </row>
     <row r="10">
@@ -650,7 +650,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>88.54</v>
+        <v>94.75</v>
       </c>
     </row>
     <row r="11">
@@ -667,7 +667,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>86.21</v>
+        <v>92.89</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.57</v>
+        <v>81.91</v>
       </c>
     </row>
     <row r="13">
@@ -701,7 +701,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>72.83</v>
+        <v>78.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:46</t>
+    <t xml:space="preserve">2026-10-05 16:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
